--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3437,7 +3437,7 @@
         <v>0.02936188255246979</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>89429</v>
@@ -6976,19 +6976,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>130908</v>
+        <v>130692</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.03492766226579176</v>
+        <v>0.03322001739267926</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>51186</v>
+        <v>51126</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -6997,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>-0.001172195522213105</v>
       </c>
       <c r="J56" t="n">
         <v>8145</v>
@@ -7019,7 +7019,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0.04746081217343478</v>
+        <v>0.04919199338903682</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -10533,7 +10533,7 @@
         <v>0.001561007816829173</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>216983</v>
@@ -10551,7 +10551,7 @@
         <v>30656</v>
       </c>
       <c r="K56" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57">
@@ -14081,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17629,7 +17629,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>6323</v>
@@ -21177,7 +21177,7 @@
         <v>-0.0006693847745390373</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>35152</v>
@@ -21195,7 +21195,7 @@
         <v>1981</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -24738,7 +24738,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28286,7 +28286,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>27735</v>
@@ -31825,16 +31825,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>96022</v>
+        <v>96019</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.002160413296456713</v>
+        <v>0.002129102958826906</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>62640</v>
@@ -31852,7 +31852,7 @@
         <v>5412</v>
       </c>
       <c r="K56" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
@@ -31868,7 +31868,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.0742017454333382</v>
+        <v>-0.07417281996271571</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -35382,7 +35382,7 @@
         <v>0.008239858635525506</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>2903</v>
@@ -35400,7 +35400,7 @@
         <v>5505</v>
       </c>
       <c r="K56" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
@@ -38930,7 +38930,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42478,7 +42478,7 @@
         <v>0.07651220865704772</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>19648</v>
@@ -46026,7 +46026,7 @@
         <v>0.06662416870542022</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>18686</v>
@@ -49574,7 +49574,7 @@
         <v>0.01097895699908509</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3437,7 +3437,7 @@
         <v>0.02936188255246979</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>89429</v>
@@ -6985,7 +6985,7 @@
         <v>0.03322001739267926</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>51126</v>
@@ -10533,7 +10533,7 @@
         <v>0.001561007816829173</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>216983</v>
@@ -14081,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17629,7 +17629,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>6323</v>
@@ -21177,7 +21177,7 @@
         <v>-0.0006693847745390373</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>35152</v>
@@ -24738,7 +24738,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28286,7 +28286,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>27735</v>
@@ -31834,7 +31834,7 @@
         <v>0.002129102958826906</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>62640</v>
@@ -35382,7 +35382,7 @@
         <v>0.008239858635525506</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>2903</v>
@@ -38930,7 +38930,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42478,7 +42478,7 @@
         <v>0.07651220865704772</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>19648</v>
@@ -46026,7 +46026,7 @@
         <v>0.06662416870542022</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>18686</v>
@@ -49574,7 +49574,7 @@
         <v>0.01097895699908509</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3446,10 +3446,10 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>30517</v>
+        <v>31780</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.5663040781415271</v>
+        <v>0.5827968503114431</v>
       </c>
       <c r="J56" t="n">
         <v>11671</v>
@@ -3486,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.6981308255381589</v>
+        <v>-0.7012763078649276</v>
       </c>
       <c r="J57" t="n">
         <v>6053</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3455,7 +3455,7 @@
         <v>11671</v>
       </c>
       <c r="K56" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57">
@@ -10551,7 +10551,7 @@
         <v>30656</v>
       </c>
       <c r="K56" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57">
@@ -31852,7 +31852,7 @@
         <v>5412</v>
       </c>
       <c r="K56" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57">
@@ -38921,13 +38921,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>6548</v>
+        <v>6613</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>0.009926695174098962</v>
       </c>
       <c r="E56" t="n">
         <v>3</v>
@@ -38964,7 +38964,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.4706780696395846</v>
+        <v>-0.4758808407681839</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -46044,7 +46044,7 @@
         <v>2991</v>
       </c>
       <c r="K56" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3437,7 +3437,7 @@
         <v>0.02936188255246979</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>89429</v>
@@ -3455,7 +3455,7 @@
         <v>11671</v>
       </c>
       <c r="K56" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="57">
@@ -6976,16 +6976,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>130692</v>
+        <v>131446</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.03322001739267926</v>
+        <v>0.03918096292197012</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>51126</v>
@@ -7019,7 +7019,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0.04919199338903682</v>
+        <v>0.04317362262830364</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -10533,7 +10533,7 @@
         <v>0.001561007816829173</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>216983</v>
@@ -10551,7 +10551,7 @@
         <v>30656</v>
       </c>
       <c r="K56" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57">
@@ -14081,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17629,7 +17629,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>6323</v>
@@ -21177,7 +21177,7 @@
         <v>-0.0006693847745390373</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>35152</v>
@@ -24738,7 +24738,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28286,7 +28286,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>27735</v>
@@ -31825,16 +31825,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>96019</v>
+        <v>96040</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.002129102958826906</v>
+        <v>0.002348275322235558</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>62640</v>
@@ -31852,7 +31852,7 @@
         <v>5412</v>
       </c>
       <c r="K56" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57">
@@ -31868,7 +31868,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.07417281996271571</v>
+        <v>-0.07437526030820492</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -35382,7 +35382,7 @@
         <v>0.008239858635525506</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>2903</v>
@@ -38930,7 +38930,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42478,7 +42478,7 @@
         <v>0.07651220865704772</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>19648</v>
@@ -46026,7 +46026,7 @@
         <v>0.06662416870542022</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>18686</v>
@@ -49574,7 +49574,7 @@
         <v>0.01097895699908509</v>
       </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3437,7 +3437,7 @@
         <v>0.02936188255246979</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>89429</v>
@@ -3455,7 +3455,7 @@
         <v>11671</v>
       </c>
       <c r="K56" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57">
@@ -6985,7 +6985,7 @@
         <v>0.03918096292197012</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>51126</v>
@@ -7003,7 +7003,7 @@
         <v>8145</v>
       </c>
       <c r="K56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">
@@ -10524,16 +10524,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>424747</v>
+        <v>424784</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.001561007816829173</v>
+        <v>0.001648254477286393</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>216983</v>
@@ -10551,7 +10551,7 @@
         <v>30656</v>
       </c>
       <c r="K56" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57">
@@ -10567,7 +10567,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.02136566002820503</v>
+        <v>-0.0214509021055407</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -14081,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17629,7 +17629,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>6323</v>
@@ -21177,7 +21177,7 @@
         <v>-0.0006693847745390373</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>35152</v>
@@ -24738,7 +24738,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28286,7 +28286,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>27735</v>
@@ -31825,16 +31825,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>96040</v>
+        <v>97916</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.002348275322235558</v>
+        <v>0.02192767312007515</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>62640</v>
@@ -31868,7 +31868,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.07437526030820492</v>
+        <v>-0.09210956329915437</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -35373,16 +35373,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>104986</v>
+        <v>104992</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.008239858635525506</v>
+        <v>0.008297480024585127</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>2903</v>
@@ -35400,7 +35400,7 @@
         <v>5505</v>
       </c>
       <c r="K56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -35416,7 +35416,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.1403329967805231</v>
+        <v>-0.1403821243523316</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -38930,7 +38930,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42478,7 +42478,7 @@
         <v>0.07651220865704772</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>19648</v>
@@ -46017,16 +46017,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>61909</v>
+        <v>62405</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.06662416870542022</v>
+        <v>0.07516970469659902</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>18686</v>
@@ -46044,7 +46044,7 @@
         <v>2991</v>
       </c>
       <c r="K56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
@@ -46060,7 +46060,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.09757870422717214</v>
+        <v>-0.104751221857223</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -49574,7 +49574,7 @@
         <v>0.01097895699908509</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3455,7 +3455,7 @@
         <v>11671</v>
       </c>
       <c r="K56" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57">
@@ -7003,7 +7003,7 @@
         <v>8145</v>
       </c>
       <c r="K56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
@@ -10551,7 +10551,7 @@
         <v>30656</v>
       </c>
       <c r="K56" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57">
@@ -31852,7 +31852,7 @@
         <v>5412</v>
       </c>
       <c r="K56" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">
@@ -35400,7 +35400,7 @@
         <v>5505</v>
       </c>
       <c r="K56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
@@ -46044,7 +46044,7 @@
         <v>2991</v>
       </c>
       <c r="K56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3455,7 +3455,7 @@
         <v>11671</v>
       </c>
       <c r="K56" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57">
@@ -7003,7 +7003,7 @@
         <v>8145</v>
       </c>
       <c r="K56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
@@ -10551,7 +10551,7 @@
         <v>30656</v>
       </c>
       <c r="K56" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57">
@@ -31852,7 +31852,7 @@
         <v>5412</v>
       </c>
       <c r="K56" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57">
@@ -35400,7 +35400,7 @@
         <v>5505</v>
       </c>
       <c r="K56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57">
@@ -46044,7 +46044,7 @@
         <v>2991</v>
       </c>
       <c r="K56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -10524,13 +10524,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>424784</v>
+        <v>424695</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.001648254477286393</v>
+        <v>0.001438390888619027</v>
       </c>
       <c r="E56" t="n">
         <v>7</v>
@@ -10551,7 +10551,7 @@
         <v>30656</v>
       </c>
       <c r="K56" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57">
@@ -10567,7 +10567,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.0214509021055407</v>
+        <v>-0.021245835246471</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -28304,7 +28304,7 @@
         <v>5368</v>
       </c>
       <c r="K56" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -7003,7 +7003,7 @@
         <v>8145</v>
       </c>
       <c r="K56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
@@ -10551,7 +10551,7 @@
         <v>30656</v>
       </c>
       <c r="K56" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57">
@@ -31852,7 +31852,7 @@
         <v>5412</v>
       </c>
       <c r="K56" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57">
@@ -46044,7 +46044,7 @@
         <v>2991</v>
       </c>
       <c r="K56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3437,7 +3437,7 @@
         <v>0.02936188255246979</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>89429</v>
@@ -6976,16 +6976,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>131446</v>
+        <v>133474</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.03918096292197012</v>
+        <v>0.05521385089730414</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>51126</v>
@@ -7019,7 +7019,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0.04317362262830364</v>
+        <v>0.02732367352443172</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -10524,16 +10524,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>424695</v>
+        <v>424541</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.001438390888619027</v>
+        <v>0.001075256139688978</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>216983</v>
@@ -10567,7 +10567,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>-0.021245835246471</v>
+        <v>-0.02089079735526133</v>
       </c>
       <c r="E57" t="n">
         <v>6</v>
@@ -14081,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17629,7 +17629,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>6323</v>
@@ -21177,7 +21177,7 @@
         <v>-0.0006693847745390373</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>35152</v>
@@ -24738,7 +24738,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28286,7 +28286,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>27735</v>
@@ -31834,7 +31834,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>62640</v>
@@ -35382,7 +35382,7 @@
         <v>0.008297480024585127</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>2903</v>
@@ -38930,7 +38930,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42478,7 +42478,7 @@
         <v>0.07651220865704772</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>19648</v>
@@ -46026,7 +46026,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>18686</v>
@@ -49574,7 +49574,7 @@
         <v>0.01097895699908509</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3437,7 +3437,7 @@
         <v>0.02936188255246979</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>89429</v>
@@ -3446,16 +3446,16 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>31780</v>
+        <v>32808</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.5827968503114431</v>
+        <v>0.5962208960681127</v>
       </c>
       <c r="J56" t="n">
-        <v>11671</v>
+        <v>11714</v>
       </c>
       <c r="K56" t="n">
-        <v>102</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57">
@@ -3486,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.7012763078649276</v>
+        <v>-0.7037885419308393</v>
       </c>
       <c r="J57" t="n">
         <v>6053</v>
@@ -6985,7 +6985,7 @@
         <v>0.05521385089730414</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>51126</v>
@@ -7000,10 +7000,10 @@
         <v>-0.001172195522213105</v>
       </c>
       <c r="J56" t="n">
-        <v>8145</v>
+        <v>8183</v>
       </c>
       <c r="K56" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
@@ -10533,7 +10533,7 @@
         <v>0.001075256139688978</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>216983</v>
@@ -10542,16 +10542,16 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>13382</v>
+        <v>13397</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.05840489219078074</v>
+        <v>0.05847380922845079</v>
       </c>
       <c r="J56" t="n">
-        <v>30656</v>
+        <v>30689</v>
       </c>
       <c r="K56" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57">
@@ -10582,7 +10582,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.5783821327024504</v>
+        <v>-0.5784095841652921</v>
       </c>
       <c r="J57" t="n">
         <v>17793</v>
@@ -14081,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17629,7 +17629,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>6323</v>
@@ -17644,10 +17644,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>3691</v>
+        <v>3695</v>
       </c>
       <c r="K56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -21177,7 +21177,7 @@
         <v>-0.0006693847745390373</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>35152</v>
@@ -21192,10 +21192,10 @@
         <v>-0.009985734664764621</v>
       </c>
       <c r="J56" t="n">
-        <v>1981</v>
+        <v>1986</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
@@ -24738,7 +24738,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -24753,10 +24753,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -28286,7 +28286,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>27735</v>
@@ -28301,10 +28301,10 @@
         <v>0.01665765278528935</v>
       </c>
       <c r="J56" t="n">
-        <v>5368</v>
+        <v>5377</v>
       </c>
       <c r="K56" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57">
@@ -31834,7 +31834,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>62640</v>
@@ -31849,10 +31849,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>5412</v>
+        <v>5455</v>
       </c>
       <c r="K56" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -35382,7 +35382,7 @@
         <v>0.008297480024585127</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>2903</v>
@@ -35397,10 +35397,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>5505</v>
+        <v>5523</v>
       </c>
       <c r="K56" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -38930,7 +38930,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -38945,10 +38945,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -42478,7 +42478,7 @@
         <v>0.07651220865704772</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>19648</v>
@@ -42493,10 +42493,10 @@
         <v>0.1193191393741925</v>
       </c>
       <c r="J56" t="n">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -46026,7 +46026,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>18686</v>
@@ -46035,16 +46035,16 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>26652</v>
+        <v>26840</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>1.427867623433651</v>
+        <v>1.437935096926207</v>
       </c>
       <c r="J56" t="n">
-        <v>2991</v>
+        <v>3004</v>
       </c>
       <c r="K56" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
@@ -46075,7 +46075,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.6670783889893688</v>
+        <v>-0.6684531915828318</v>
       </c>
       <c r="J57" t="n">
         <v>1155</v>
@@ -49574,7 +49574,7 @@
         <v>0.01097895699908509</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -49589,10 +49589,10 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3437,7 +3437,7 @@
         <v>0.02936188255246979</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>89429</v>
@@ -6985,7 +6985,7 @@
         <v>0.05521385089730414</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>51126</v>
@@ -10533,7 +10533,7 @@
         <v>0.001075256139688978</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>216983</v>
@@ -14081,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17629,7 +17629,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>6323</v>
@@ -21177,7 +21177,7 @@
         <v>-0.0006693847745390373</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>35152</v>
@@ -24738,7 +24738,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28286,7 +28286,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>27735</v>
@@ -31834,7 +31834,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>62640</v>
@@ -35382,7 +35382,7 @@
         <v>0.008297480024585127</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>2903</v>
@@ -38930,7 +38930,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42478,7 +42478,7 @@
         <v>0.07651220865704772</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>19648</v>
@@ -46026,7 +46026,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>18686</v>
@@ -49574,7 +49574,7 @@
         <v>0.01097895699908509</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3437,7 +3437,7 @@
         <v>0.02936188255246979</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>89429</v>
@@ -6985,7 +6985,7 @@
         <v>0.05521385089730414</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>51126</v>
@@ -10533,7 +10533,7 @@
         <v>0.001075256139688978</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>216983</v>
@@ -14081,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17629,7 +17629,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>6323</v>
@@ -21177,7 +21177,7 @@
         <v>-0.0006693847745390373</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>35152</v>
@@ -24738,7 +24738,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28286,7 +28286,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>27735</v>
@@ -31834,7 +31834,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>62640</v>
@@ -35382,19 +35382,19 @@
         <v>0.008297480024585127</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
-        <v>2903</v>
+        <v>86</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>43354</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0</v>
+        <v>13.96383052015157</v>
       </c>
       <c r="J56" t="n">
         <v>5523</v>
@@ -35431,7 +35431,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.00826730967964175</v>
+        <v>-0.9337246777163904</v>
       </c>
       <c r="J57" t="n">
         <v>410</v>
@@ -38930,7 +38930,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42478,7 +42478,7 @@
         <v>0.07651220865704772</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>19648</v>
@@ -46026,7 +46026,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>18686</v>
@@ -49574,7 +49574,7 @@
         <v>0.01097895699908509</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3437,7 +3437,7 @@
         <v>0.02936188255246979</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>89429</v>
@@ -6985,7 +6985,7 @@
         <v>0.05521385089730414</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>51126</v>
@@ -10533,7 +10533,7 @@
         <v>0.001075256139688978</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>216983</v>
@@ -14081,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -17629,16 +17629,16 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
-        <v>6323</v>
+        <v>8026</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>49432</v>
+        <v>62319</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>0</v>
@@ -17678,7 +17678,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>-0.9648641377454937</v>
+        <v>-0.9721515388442675</v>
       </c>
       <c r="J57" t="n">
         <v>659</v>
@@ -21177,7 +21177,7 @@
         <v>-0.0006693847745390373</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>35152</v>
@@ -24738,7 +24738,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -28286,7 +28286,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>27735</v>
@@ -31834,7 +31834,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>62640</v>
@@ -35382,7 +35382,7 @@
         <v>0.008297480024585127</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>86</v>
@@ -38930,7 +38930,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -42478,7 +42478,7 @@
         <v>0.07651220865704772</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>19648</v>
@@ -46026,7 +46026,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>18686</v>
@@ -46041,7 +46041,7 @@
         <v>1.437935096926207</v>
       </c>
       <c r="J56" t="n">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="K56" t="n">
         <v>14</v>
@@ -49574,7 +49574,7 @@
         <v>0.01097895699908509</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3751,7 +3751,7 @@
         <v>11714</v>
       </c>
       <c r="K64" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65">
@@ -10921,7 +10921,7 @@
         <v>30689</v>
       </c>
       <c r="K64" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65">
@@ -32444,7 +32444,7 @@
         <v>5455</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -36029,7 +36029,7 @@
         <v>5523</v>
       </c>
       <c r="K64" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
@@ -46784,7 +46784,7 @@
         <v>3002</v>
       </c>
       <c r="K64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3751,7 +3751,7 @@
         <v>11714</v>
       </c>
       <c r="K64" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65">
@@ -10921,7 +10921,7 @@
         <v>30689</v>
       </c>
       <c r="K64" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65">
@@ -32444,7 +32444,7 @@
         <v>5455</v>
       </c>
       <c r="K64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
@@ -36029,7 +36029,7 @@
         <v>5523</v>
       </c>
       <c r="K64" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3751,7 +3751,7 @@
         <v>11714</v>
       </c>
       <c r="K64" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65">
@@ -10921,7 +10921,7 @@
         <v>30689</v>
       </c>
       <c r="K64" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65">
@@ -32444,7 +32444,7 @@
         <v>5455</v>
       </c>
       <c r="K64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3733,7 +3733,7 @@
         <v>0.0003662710176611306</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>89429</v>
@@ -3751,7 +3751,7 @@
         <v>11714</v>
       </c>
       <c r="K64" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65">
@@ -7318,7 +7318,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>51126</v>
@@ -10894,16 +10894,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>424541</v>
+        <v>430174</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.0003628763369283225</v>
+        <v>0.0136361387130143</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>216983</v>
@@ -10921,7 +10921,7 @@
         <v>30689</v>
       </c>
       <c r="K64" t="n">
-        <v>101</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65">
@@ -10937,7 +10937,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.0206246275389185</v>
+        <v>-0.03344925541757521</v>
       </c>
       <c r="E65" t="n">
         <v>18</v>
@@ -14488,7 +14488,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -18073,7 +18073,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>8026</v>
@@ -18091,7 +18091,7 @@
         <v>3695</v>
       </c>
       <c r="K64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -21658,7 +21658,7 @@
         <v>-0.0007605950895981016</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>35152</v>
@@ -25256,7 +25256,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28841,7 +28841,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>27735</v>
@@ -32426,7 +32426,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>62640</v>
@@ -32444,7 +32444,7 @@
         <v>5455</v>
       </c>
       <c r="K64" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65">
@@ -36011,25 +36011,25 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>86</v>
+        <v>1926</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>43354</v>
+        <v>93632</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>13.96383052015157</v>
+        <v>31.91698243196693</v>
       </c>
       <c r="J64" t="n">
         <v>5523</v>
       </c>
       <c r="K64" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65">
@@ -36060,7 +36060,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.9337246777163904</v>
+        <v>-0.9698717009564871</v>
       </c>
       <c r="J65" t="n">
         <v>410</v>
@@ -39596,7 +39596,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -43172,16 +43172,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>15519</v>
+        <v>15539</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.07651220865704772</v>
+        <v>0.07789955604883463</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>19648</v>
@@ -43215,7 +43215,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>-0.1416328371673433</v>
+        <v>-0.1427376279039835</v>
       </c>
       <c r="E65" t="n">
         <v>18</v>
@@ -46766,7 +46766,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>18686</v>
@@ -46784,7 +46784,7 @@
         <v>3002</v>
       </c>
       <c r="K64" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
@@ -50351,7 +50351,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3751,7 +3751,7 @@
         <v>11714</v>
       </c>
       <c r="K64" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65">
@@ -10921,7 +10921,7 @@
         <v>30689</v>
       </c>
       <c r="K64" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65">
@@ -36029,7 +36029,7 @@
         <v>5523</v>
       </c>
       <c r="K64" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -10921,7 +10921,7 @@
         <v>30689</v>
       </c>
       <c r="K64" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65">
@@ -28859,7 +28859,7 @@
         <v>5377</v>
       </c>
       <c r="K64" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3733,7 +3733,7 @@
         <v>0.0003662710176611306</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>89429</v>
@@ -3751,7 +3751,7 @@
         <v>11714</v>
       </c>
       <c r="K64" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65">
@@ -7318,7 +7318,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>51126</v>
@@ -7336,7 +7336,7 @@
         <v>8183</v>
       </c>
       <c r="K64" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -10903,7 +10903,7 @@
         <v>0.0136361387130143</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>216983</v>
@@ -10921,7 +10921,7 @@
         <v>30689</v>
       </c>
       <c r="K64" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="65">
@@ -14488,7 +14488,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -18073,7 +18073,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>8026</v>
@@ -21658,7 +21658,7 @@
         <v>-0.0007605950895981016</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>35152</v>
@@ -21676,7 +21676,7 @@
         <v>1986</v>
       </c>
       <c r="K64" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
@@ -25256,7 +25256,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28841,7 +28841,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>27735</v>
@@ -32426,7 +32426,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>62640</v>
@@ -32444,7 +32444,7 @@
         <v>5455</v>
       </c>
       <c r="K64" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
@@ -36011,25 +36011,25 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
-        <v>1926</v>
+        <v>5327</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>93632</v>
+        <v>94788</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>31.91698243196693</v>
+        <v>33.48673785738891</v>
       </c>
       <c r="J64" t="n">
         <v>5523</v>
       </c>
       <c r="K64" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65">
@@ -36060,7 +36060,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.9698717009564871</v>
+        <v>-0.9712430704689607</v>
       </c>
       <c r="J65" t="n">
         <v>410</v>
@@ -39596,7 +39596,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -43181,7 +43181,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>19648</v>
@@ -46766,7 +46766,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>18686</v>
@@ -50351,7 +50351,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3733,7 +3733,7 @@
         <v>0.0003662710176611306</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>89429</v>
@@ -3751,7 +3751,7 @@
         <v>11714</v>
       </c>
       <c r="K64" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65">
@@ -7318,7 +7318,7 @@
         <v>0.04932389937106918</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>51126</v>
@@ -7336,7 +7336,7 @@
         <v>8183</v>
       </c>
       <c r="K64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
@@ -10903,7 +10903,7 @@
         <v>0.0136361387130143</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>216983</v>
@@ -10921,7 +10921,7 @@
         <v>30689</v>
       </c>
       <c r="K64" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65">
@@ -14488,7 +14488,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -18073,7 +18073,7 @@
         <v>-0.001378347727470994</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>8026</v>
@@ -18091,7 +18091,7 @@
         <v>3695</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -21658,7 +21658,7 @@
         <v>-0.0007605950895981016</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>35152</v>
@@ -25256,7 +25256,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28841,7 +28841,7 @@
         <v>0.002034258467438908</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>27735</v>
@@ -32426,7 +32426,7 @@
         <v>0.02192767312007515</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>62640</v>
@@ -36011,7 +36011,7 @@
         <v>0.008278113896091423</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>5327</v>
@@ -36029,7 +36029,7 @@
         <v>5523</v>
       </c>
       <c r="K64" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65">
@@ -39596,7 +39596,7 @@
         <v>0.009926695174098962</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -43181,7 +43181,7 @@
         <v>0.07789955604883463</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>19648</v>
@@ -46766,7 +46766,7 @@
         <v>0.07516970469659902</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>18686</v>
@@ -50351,7 +50351,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -50369,7 +50369,7 @@
         <v>424</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -7336,7 +7336,7 @@
         <v>8183</v>
       </c>
       <c r="K64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">
@@ -36029,7 +36029,7 @@
         <v>5523</v>
       </c>
       <c r="K64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">
@@ -43199,7 +43199,7 @@
         <v>784</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroNVR.xlsx
+++ b/regionais/registroNVR.xlsx
@@ -3751,7 +3751,7 @@
         <v>11714</v>
       </c>
       <c r="K64" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65">
@@ -7336,7 +7336,7 @@
         <v>8183</v>
       </c>
       <c r="K64" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
@@ -10921,7 +10921,7 @@
         <v>30689</v>
       </c>
       <c r="K64" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="65">
@@ -18091,7 +18091,7 @@
         <v>3695</v>
       </c>
       <c r="K64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -21676,7 +21676,7 @@
         <v>1986</v>
       </c>
       <c r="K64" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
@@ -32444,7 +32444,7 @@
         <v>5455</v>
       </c>
       <c r="K64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65">
@@ -36029,7 +36029,7 @@
         <v>5523</v>
       </c>
       <c r="K64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65">
@@ -46784,7 +46784,7 @@
         <v>3002</v>
       </c>
       <c r="K64" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
